--- a/config/水冷机组_埃森特.xlsx
+++ b/config/水冷机组_埃森特.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18569" windowHeight="11268"/>
+    <workbookView windowWidth="18569" windowHeight="11268" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="遥测" sheetId="1" r:id="rId1"/>
@@ -487,7 +487,8 @@
   <si>
     <t>0 自动|Auto
 1 制冷|Cooling
-2 制热|Heating</t>
+2 制热|Heating
+3 自循环|Circulation</t>
   </si>
   <si>
     <t>制冷设定出水温度</t>
@@ -603,7 +604,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -613,13 +614,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1074,152 +1068,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1227,9 +1221,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1237,9 +1228,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1594,1471 +1582,1471 @@
   <dimension ref="A1:P29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="9" style="6"/>
-    <col min="2" max="2" width="32.0634920634921" style="6" customWidth="1"/>
-    <col min="3" max="3" width="8.30952380952381" style="6" customWidth="1"/>
-    <col min="4" max="4" width="9" style="6"/>
-    <col min="5" max="5" width="48.7539682539683" style="6" customWidth="1"/>
-    <col min="6" max="6" width="10.1031746031746" style="6" customWidth="1"/>
-    <col min="7" max="7" width="14.3888888888889" style="6" customWidth="1"/>
-    <col min="8" max="8" width="9" style="6"/>
-    <col min="9" max="9" width="10.8412698412698" style="6" customWidth="1"/>
-    <col min="10" max="10" width="4.84920634920635" style="6" customWidth="1"/>
-    <col min="11" max="11" width="6.57936507936508" style="6" customWidth="1"/>
-    <col min="12" max="12" width="4.84920634920635" style="6" customWidth="1"/>
-    <col min="13" max="13" width="46.6587301587302" style="6" customWidth="1"/>
-    <col min="14" max="14" width="56.8571428571429" style="6" customWidth="1"/>
-    <col min="15" max="16" width="57.8412698412698" style="6" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="32.0634920634921" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.30952380952381" style="5" customWidth="1"/>
+    <col min="4" max="4" width="9" style="5"/>
+    <col min="5" max="5" width="48.7539682539683" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.1031746031746" style="5" customWidth="1"/>
+    <col min="7" max="7" width="14.3888888888889" style="5" customWidth="1"/>
+    <col min="8" max="8" width="9" style="5"/>
+    <col min="9" max="9" width="10.8412698412698" style="5" customWidth="1"/>
+    <col min="10" max="10" width="4.84920634920635" style="5" customWidth="1"/>
+    <col min="11" max="11" width="6.57936507936508" style="5" customWidth="1"/>
+    <col min="12" max="12" width="4.84920634920635" style="5" customWidth="1"/>
+    <col min="13" max="13" width="46.6587301587302" style="5" customWidth="1"/>
+    <col min="14" max="14" width="56.8571428571429" style="5" customWidth="1"/>
+    <col min="15" max="16" width="57.8412698412698" style="5" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" spans="1:16">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+    <row r="1" s="4" customFormat="1" spans="1:16">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="5">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="6">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="5">
+        <v>1</v>
+      </c>
+      <c r="G2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="6">
-        <v>1</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" s="6">
+      <c r="H2" s="5">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" s="5">
         <v>0.1</v>
       </c>
-      <c r="K2" s="6">
-        <v>0</v>
-      </c>
-      <c r="L2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="6" t="s">
+      <c r="K2" s="5">
+        <v>0</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="6" t="s">
+      <c r="O2" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="6">
+      <c r="A3" s="5">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="E3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="5">
         <v>2</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="6">
-        <v>1</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" s="6">
+      <c r="H3" s="5">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="5">
         <v>0.1</v>
       </c>
-      <c r="K3" s="6">
-        <v>0</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" s="6" t="s">
+      <c r="K3" s="5">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P3" s="6" t="s">
+      <c r="O3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="6">
+      <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="E4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="5">
         <v>3</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="6">
-        <v>1</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4" s="6">
+      <c r="H4" s="5">
+        <v>1</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="5">
         <v>0.1</v>
       </c>
-      <c r="K4" s="6">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" s="6" t="s">
+      <c r="K4" s="5">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="O4" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P4" s="6" t="s">
+      <c r="O4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P4" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="6">
+      <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="6">
+      <c r="E5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="5">
         <v>4</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="6">
-        <v>1</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="6">
-        <v>1</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="6" t="s">
+      <c r="H5" s="5">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P5" s="6" t="s">
+      <c r="O5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P5" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="6">
+      <c r="A6" s="5">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="6">
+      <c r="E6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="5">
         <v>5</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J6" s="6">
-        <v>1</v>
-      </c>
-      <c r="K6" s="6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="6" t="s">
+      <c r="H6" s="5">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>0</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="O6" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P6" s="6" t="s">
+      <c r="O6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="6">
+      <c r="A7" s="5">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="D7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>17</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="6">
-        <v>1</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="6">
-        <v>1</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" s="6" t="s">
+      <c r="H7" s="5">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>0</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="O7" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P7" s="6" t="s">
+      <c r="O7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P7" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="6">
+      <c r="A8" s="5">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>18</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="6">
-        <v>1</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J8" s="6">
-        <v>1</v>
-      </c>
-      <c r="K8" s="6">
-        <v>0</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" s="6" t="s">
+      <c r="H8" s="5">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M8" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="O8" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P8" s="6" t="s">
+      <c r="O8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P8" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="6">
+      <c r="A9" s="5">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F9" s="6">
-        <v>19</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="E9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="5">
+        <v>19</v>
+      </c>
+      <c r="G9" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="6">
-        <v>1</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J9" s="6">
-        <v>1</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M9" s="6" t="s">
+      <c r="H9" s="5">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="O9" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P9" s="6" t="s">
+      <c r="O9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P9" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="6">
+      <c r="A10" s="5">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>20</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H10" s="6">
-        <v>1</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J10" s="6">
-        <v>1</v>
-      </c>
-      <c r="K10" s="6">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M10" s="6" t="s">
+      <c r="H10" s="5">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5">
+        <v>0</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M10" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="O10" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" ht="378" spans="1:16">
-      <c r="A11" s="6">
+      <c r="O10" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P10" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" ht="144" spans="1:16">
+      <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="6">
-        <v>21</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="D11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="5">
+        <v>21</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H11" s="6">
-        <v>1</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="6">
-        <v>1</v>
-      </c>
-      <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M11" s="6" t="s">
+      <c r="H11" s="5">
+        <v>1</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M11" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="P11" s="6" t="s">
+      <c r="P11" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" s="6">
+      <c r="A12" s="5">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="E12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="5">
         <v>22</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="6">
-        <v>1</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J12" s="6">
-        <v>1</v>
-      </c>
-      <c r="K12" s="6">
-        <v>0</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" s="6" t="s">
+      <c r="H12" s="5">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5">
+        <v>0</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M12" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="O12" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P12" s="6" t="s">
+      <c r="O12" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P12" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" s="6">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F13" s="6">
+      <c r="E13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F13" s="5">
         <v>23</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="6">
-        <v>1</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="6">
-        <v>1</v>
-      </c>
-      <c r="K13" s="6">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M13" s="6" t="s">
+      <c r="H13" s="5">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5">
+        <v>0</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M13" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="O13" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P13" s="6" t="s">
+      <c r="O13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P13" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" s="6">
+      <c r="A14" s="5">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="6">
+      <c r="D14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F14" s="5">
         <v>28</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="6">
-        <v>1</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="6">
-        <v>1</v>
-      </c>
-      <c r="K14" s="6">
-        <v>0</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M14" s="6" t="s">
+      <c r="H14" s="5">
+        <v>1</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="5">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5">
+        <v>0</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="N14" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="O14" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" ht="378" spans="1:16">
-      <c r="A15" s="6">
+      <c r="O14" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P14" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" ht="144" spans="1:16">
+      <c r="A15" s="5">
         <v>14</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="D15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F15" s="5">
         <v>37</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="6">
-        <v>1</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="6">
-        <v>1</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" s="6" t="s">
+      <c r="H15" s="5">
+        <v>1</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5">
+        <v>0</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="N15" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="O15" s="8" t="s">
+      <c r="O15" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="P15" s="6" t="s">
+      <c r="P15" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" s="6">
+      <c r="A16" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="6">
+      <c r="E16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="5">
         <v>38</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="6">
-        <v>1</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J16" s="6">
-        <v>1</v>
-      </c>
-      <c r="K16" s="6">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M16" s="6" t="s">
+      <c r="H16" s="5">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="5">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="N16" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="O16" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P16" s="6" t="s">
+      <c r="O16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P16" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" s="6">
+      <c r="A17" s="5">
         <v>16</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="E17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F17" s="5">
         <v>39</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="6">
-        <v>1</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J17" s="6">
-        <v>1</v>
-      </c>
-      <c r="K17" s="6">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M17" s="6" t="s">
+      <c r="H17" s="5">
+        <v>1</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="5">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="N17" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="O17" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P17" s="6" t="s">
+      <c r="O17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P17" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" s="6">
+      <c r="A18" s="5">
         <v>17</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="6">
+      <c r="D18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="5">
         <v>44</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="6">
-        <v>1</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J18" s="6">
-        <v>1</v>
-      </c>
-      <c r="K18" s="6">
-        <v>0</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" s="6" t="s">
+      <c r="H18" s="5">
+        <v>1</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="5">
+        <v>1</v>
+      </c>
+      <c r="K18" s="5">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="N18" s="6" t="s">
+      <c r="N18" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="O18" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P18" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" ht="90" spans="1:16">
-      <c r="A19" s="6">
+      <c r="O18" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" ht="72" spans="1:16">
+      <c r="A19" s="5">
         <v>18</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="6">
+      <c r="D19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F19" s="5">
         <v>45</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="6">
-        <v>1</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J19" s="6">
-        <v>1</v>
-      </c>
-      <c r="K19" s="6">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M19" s="6" t="s">
+      <c r="H19" s="5">
+        <v>1</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" s="5">
+        <v>1</v>
+      </c>
+      <c r="K19" s="5">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M19" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="N19" s="6" t="s">
+      <c r="N19" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="O19" s="8" t="s">
+      <c r="O19" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="P19" s="6" t="s">
+      <c r="P19" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" s="6">
-        <v>19</v>
-      </c>
-      <c r="B20" s="6" t="s">
+      <c r="A20" s="5">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F20" s="6">
+      <c r="E20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F20" s="5">
         <v>46</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="6">
-        <v>1</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J20" s="6">
-        <v>1</v>
-      </c>
-      <c r="K20" s="6">
-        <v>0</v>
-      </c>
-      <c r="L20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M20" s="6" t="s">
+      <c r="H20" s="5">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" s="5">
+        <v>1</v>
+      </c>
+      <c r="K20" s="5">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M20" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="N20" s="6" t="s">
+      <c r="N20" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="O20" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P20" s="6" t="s">
+      <c r="O20" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P20" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" ht="288" spans="1:16">
-      <c r="A21" s="6">
+      <c r="A21" s="5">
         <v>20</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="6">
+      <c r="D21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F21" s="5">
         <v>59</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="6">
-        <v>1</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J21" s="6">
-        <v>1</v>
-      </c>
-      <c r="K21" s="6">
-        <v>0</v>
-      </c>
-      <c r="L21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M21" s="6" t="s">
+      <c r="H21" s="5">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="5">
+        <v>1</v>
+      </c>
+      <c r="K21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M21" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="N21" s="6" t="s">
+      <c r="N21" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="O21" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P21" s="8" t="s">
+      <c r="O21" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P21" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="22" ht="288" spans="1:16">
-      <c r="A22" s="6">
-        <v>21</v>
-      </c>
-      <c r="B22" s="6" t="s">
+      <c r="A22" s="5">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="6">
+      <c r="D22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="5">
         <v>60</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="6">
-        <v>1</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="6">
-        <v>1</v>
-      </c>
-      <c r="K22" s="6">
-        <v>0</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M22" s="6" t="s">
+      <c r="H22" s="5">
+        <v>1</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="5">
+        <v>1</v>
+      </c>
+      <c r="K22" s="5">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M22" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="N22" s="6" t="s">
+      <c r="N22" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="O22" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P22" s="8" t="s">
+      <c r="O22" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P22" s="6" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="23" ht="378" spans="1:16">
-      <c r="A23" s="6">
+      <c r="A23" s="5">
         <v>22</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F23" s="6">
+      <c r="D23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F23" s="5">
         <v>61</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="6">
-        <v>1</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J23" s="6">
-        <v>1</v>
-      </c>
-      <c r="K23" s="6">
-        <v>0</v>
-      </c>
-      <c r="L23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M23" s="6" t="s">
+      <c r="H23" s="5">
+        <v>1</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="5">
+        <v>1</v>
+      </c>
+      <c r="K23" s="5">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M23" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="N23" s="6" t="s">
+      <c r="N23" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="O23" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P23" s="8" t="s">
+      <c r="O23" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P23" s="6" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="24" ht="288" spans="1:16">
-      <c r="A24" s="6">
+      <c r="A24" s="5">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F24" s="6">
+      <c r="D24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="5">
         <v>62</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H24" s="6">
-        <v>1</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J24" s="6">
-        <v>1</v>
-      </c>
-      <c r="K24" s="6">
-        <v>0</v>
-      </c>
-      <c r="L24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M24" s="6" t="s">
+      <c r="H24" s="5">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="5">
+        <v>1</v>
+      </c>
+      <c r="K24" s="5">
+        <v>0</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M24" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="N24" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="O24" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P24" s="8" t="s">
+      <c r="O24" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P24" s="6" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F25" s="6">
+      <c r="D25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="5">
         <v>63</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="6">
-        <v>1</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J25" s="6">
-        <v>1</v>
-      </c>
-      <c r="K25" s="6">
-        <v>0</v>
-      </c>
-      <c r="L25" s="6">
-        <v>0</v>
-      </c>
-      <c r="M25" s="6" t="s">
+      <c r="H25" s="5">
+        <v>1</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="5">
+        <v>1</v>
+      </c>
+      <c r="K25" s="5">
+        <v>0</v>
+      </c>
+      <c r="L25" s="5">
+        <v>0</v>
+      </c>
+      <c r="M25" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="N25" s="6" t="s">
+      <c r="N25" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="O25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P25" s="6" t="s">
+      <c r="O25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P25" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" s="6">
+      <c r="A26" s="5">
         <v>25</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="D26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="5">
         <v>69</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="6">
-        <v>1</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J26" s="6">
-        <v>1</v>
-      </c>
-      <c r="K26" s="6">
-        <v>0</v>
-      </c>
-      <c r="L26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M26" s="6" t="s">
+      <c r="H26" s="5">
+        <v>1</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="5">
+        <v>1</v>
+      </c>
+      <c r="K26" s="5">
+        <v>0</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M26" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="N26" s="6" t="s">
+      <c r="N26" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="O26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P26" s="6" t="s">
+      <c r="O26" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P26" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" s="6">
+      <c r="A27" s="5">
         <v>26</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>70</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="6">
-        <v>1</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J27" s="6">
-        <v>1</v>
-      </c>
-      <c r="K27" s="6">
-        <v>0</v>
-      </c>
-      <c r="L27" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M27" s="6" t="s">
+      <c r="H27" s="5">
+        <v>1</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1</v>
+      </c>
+      <c r="K27" s="5">
+        <v>0</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M27" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="N27" s="6" t="s">
+      <c r="N27" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="O27" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P27" s="6" t="s">
+      <c r="O27" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P27" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" s="6">
+      <c r="A28" s="5">
         <v>27</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F28" s="6">
+      <c r="E28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="5">
         <v>71</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H28" s="6">
-        <v>1</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J28" s="6">
-        <v>1</v>
-      </c>
-      <c r="K28" s="6">
-        <v>0</v>
-      </c>
-      <c r="L28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M28" s="6" t="s">
+      <c r="H28" s="5">
+        <v>1</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J28" s="5">
+        <v>1</v>
+      </c>
+      <c r="K28" s="5">
+        <v>0</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M28" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="N28" s="6" t="s">
+      <c r="N28" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="O28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P28" s="6" t="s">
+      <c r="O28" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P28" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" s="6">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="E29" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="5">
         <v>72</v>
       </c>
-      <c r="G29" s="6" t="s">
+      <c r="G29" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="6">
-        <v>1</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="J29" s="6">
-        <v>1</v>
-      </c>
-      <c r="K29" s="6">
-        <v>0</v>
-      </c>
-      <c r="L29" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M29" s="6" t="s">
+      <c r="H29" s="5">
+        <v>1</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="5">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5">
+        <v>0</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="M29" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="N29" s="6" t="s">
+      <c r="N29" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="O29" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="P29" s="6" t="s">
+      <c r="O29" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="P29" s="5" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3087,52 +3075,52 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:16">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3179,14 +3167,14 @@
       <c r="N2" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="3" t="s">
         <v>124</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" ht="54" spans="1:16">
+    <row r="3" ht="72" spans="1:16">
       <c r="A3" s="2">
         <v>2001</v>
       </c>
@@ -3229,7 +3217,7 @@
       <c r="N3" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="3" t="s">
         <v>128</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -3729,7 +3717,7 @@
       <c r="N13" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="O13" s="4" t="s">
+      <c r="O13" s="3" t="s">
         <v>159</v>
       </c>
       <c r="P13" s="2" t="s">
